--- a/outputs/daily/hr_rankings_2026-09-05_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-05_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
